--- a/data/performance/daily/signal_list_2026-05-21.xlsx
+++ b/data/performance/daily/signal_list_2026-05-21.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 27.3%  (3W / 8L of 11 evaluated)</t>
+          <t>Win Rate: 36.4%  (4W / 7L of 11 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1555</v>
+        <v>1570</v>
       </c>
       <c r="D5" t="n">
         <v>1345</v>
@@ -553,10 +553,10 @@
         <v>1635</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>5.14</v>
+        <v>4.14</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-13.5</v>
+        <v>-14.33</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
         <v>151</v>
@@ -595,14 +595,14 @@
         <v>152</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.66</v>
+        <v>1.33</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>0.67</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1495</v>
+        <v>1485</v>
       </c>
       <c r="D8" t="n">
         <v>1505</v>
@@ -679,10 +679,10 @@
         <v>1505</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.67</v>
+        <v>1.35</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.67</v>
+        <v>1.35</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2530</v>
+        <v>2550</v>
       </c>
       <c r="D9" t="n">
         <v>2510</v>
@@ -721,10 +721,10 @@
         <v>2540</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.39</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.79</v>
+        <v>-1.57</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6550</v>
+        <v>6500</v>
       </c>
       <c r="D11" t="n">
         <v>6700</v>
@@ -805,10 +805,10 @@
         <v>7100</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>8.4</v>
+        <v>9.23</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2.29</v>
+        <v>3.08</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
         <v>36</v>
@@ -847,10 +847,10 @@
         <v>36</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D13" t="n">
         <v>408</v>
@@ -889,10 +889,10 @@
         <v>420</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.48</v>
+        <v>0.96</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.39</v>
+        <v>-1.92</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D14" t="n">
         <v>282</v>
@@ -931,10 +931,10 @@
         <v>310</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3.33</v>
+        <v>2.65</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6</v>
+        <v>-6.62</v>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="D15" t="n">
         <v>288</v>
@@ -973,10 +973,10 @@
         <v>378</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>18.87</v>
+        <v>11.83</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-9.43</v>
+        <v>-14.79</v>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-21.xlsx
+++ b/data/performance/daily/signal_list_2026-05-21.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-05-21</t>
+          <t>Swing — Review sesi market 2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 36.4%  (4W / 7L of 11 evaluated)</t>
+          <t>Win Rate: 21.4%  (12W / 44L of 56 evaluated)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APIC.JK</t>
+          <t>AKRA.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1570</v>
+        <v>1390</v>
       </c>
       <c r="D5" t="n">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="E5" t="n">
-        <v>1635</v>
+        <v>1405</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>4.14</v>
+        <v>1.08</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-14.33</v>
+        <v>-3.6</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DMAS.JK</t>
+          <t>AUTO.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>150</v>
+        <v>2550</v>
       </c>
       <c r="D6" t="n">
-        <v>151</v>
+        <v>2540</v>
       </c>
       <c r="E6" t="n">
-        <v>152</v>
+        <v>2620</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.33</v>
+        <v>2.75</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-0.39</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GGRM.JK</t>
+          <t>BDMN.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -628,19 +628,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16200</v>
+        <v>4740</v>
       </c>
       <c r="D7" t="n">
-        <v>15800</v>
+        <v>4620</v>
       </c>
       <c r="E7" t="n">
-        <v>16200</v>
+        <v>4860</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.47</v>
+        <v>-2.53</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -661,28 +661,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>BRAM.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRE_MARKUP</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1485</v>
+        <v>4740</v>
       </c>
       <c r="D8" t="n">
-        <v>1505</v>
+        <v>4770</v>
       </c>
       <c r="E8" t="n">
-        <v>1505</v>
+        <v>4790</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.35</v>
+        <v>1.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.35</v>
+        <v>0.63</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>BTPN.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2550</v>
+        <v>2300</v>
       </c>
       <c r="D9" t="n">
-        <v>2510</v>
+        <v>2370</v>
       </c>
       <c r="E9" t="n">
-        <v>2540</v>
+        <v>2370</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.39</v>
+        <v>3.04</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.04</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MARK.JK</t>
+          <t>CFIN.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,28 +754,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>795</v>
+        <v>340</v>
       </c>
       <c r="D10" t="n">
-        <v>810</v>
+        <v>332</v>
       </c>
       <c r="E10" t="n">
-        <v>810</v>
+        <v>344</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.89</v>
+        <v>1.18</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-2.35</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MORA.JK</t>
+          <t>CINT.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -796,28 +796,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6500</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>6700</v>
+        <v>176</v>
       </c>
       <c r="E11" t="n">
-        <v>7100</v>
+        <v>195</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9.23</v>
+        <v>4.28</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
+        <v>-5.88</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PURA.JK</t>
+          <t>DMAS.JK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="E12" t="n">
-        <v>36</v>
+        <v>155</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-10</v>
+        <v>1.97</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-10</v>
+        <v>-1.32</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>DYAN.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>416</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>408</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>420</v>
+        <v>85</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.92</v>
+        <v>-9.41</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PACK.JK</t>
+          <t>EPMT.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -922,28 +922,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>302</v>
+        <v>2230</v>
       </c>
       <c r="D14" t="n">
-        <v>282</v>
+        <v>2260</v>
       </c>
       <c r="E14" t="n">
-        <v>310</v>
+        <v>2260</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.62</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>1.35</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -955,40 +955,1930 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>GGRM.JK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>16350</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16200</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16650</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GSMF.JK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>113</v>
+      </c>
+      <c r="D16" t="n">
+        <v>97</v>
+      </c>
+      <c r="E16" t="n">
+        <v>115</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-14.16</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ISAT.JK</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2080</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-3.26</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KONI.JK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2820</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2680</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2960</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MAPI.JK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1480</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1485</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1495</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PGLI.JK</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>208</v>
+      </c>
+      <c r="D20" t="n">
+        <v>208</v>
+      </c>
+      <c r="E20" t="n">
+        <v>228</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RELI.JK</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>510</v>
+      </c>
+      <c r="D21" t="n">
+        <v>486</v>
+      </c>
+      <c r="E21" t="n">
+        <v>510</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JGLE.JK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>78</v>
+      </c>
+      <c r="D22" t="n">
+        <v>71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>71</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>POWR.JK</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>710.47</v>
+      </c>
+      <c r="D23" t="n">
+        <v>715</v>
+      </c>
+      <c r="E23" t="n">
+        <v>730</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PRDA.JK</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2630</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2550</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2640</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-3.04</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MORA.JK</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>7125</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6500</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8475</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PBID.JK</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>502</v>
+      </c>
+      <c r="D26" t="n">
+        <v>478</v>
+      </c>
+      <c r="E26" t="n">
+        <v>500</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>-4.78</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DFAM.JK</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>100</v>
+      </c>
+      <c r="D27" t="n">
+        <v>109</v>
+      </c>
+      <c r="E27" t="n">
+        <v>111</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PRIM.JK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>88</v>
+      </c>
+      <c r="D28" t="n">
+        <v>87</v>
+      </c>
+      <c r="E28" t="n">
+        <v>96</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BPTR.JK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>79</v>
+      </c>
+      <c r="D29" t="n">
+        <v>71</v>
+      </c>
+      <c r="E29" t="n">
+        <v>80</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-10.13</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LUCK.JK</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>111</v>
+      </c>
+      <c r="D30" t="n">
+        <v>108</v>
+      </c>
+      <c r="E30" t="n">
+        <v>113</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SFAN.JK</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1955</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1955</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1955</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>KJEN.JK</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>162</v>
+      </c>
+      <c r="D32" t="n">
+        <v>174</v>
+      </c>
+      <c r="E32" t="n">
+        <v>200</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>23.46</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SMKL.JK</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>161</v>
+      </c>
+      <c r="D33" t="n">
+        <v>155</v>
+      </c>
+      <c r="E33" t="n">
+        <v>164</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-3.73</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>GGRP.JK</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>326</v>
+      </c>
+      <c r="D34" t="n">
+        <v>322</v>
+      </c>
+      <c r="E34" t="n">
+        <v>332</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PGJO.JK</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>800</v>
+      </c>
+      <c r="D35" t="n">
+        <v>720</v>
+      </c>
+      <c r="E35" t="n">
+        <v>775</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PURA.JK</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>44</v>
+      </c>
+      <c r="D36" t="n">
+        <v>40</v>
+      </c>
+      <c r="E36" t="n">
+        <v>44</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-9.09</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TAMA.JK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>218</v>
+      </c>
+      <c r="D37" t="n">
+        <v>197</v>
+      </c>
+      <c r="E37" t="n">
+        <v>214</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>-1.83</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PPGL.JK</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>197</v>
+      </c>
+      <c r="D38" t="n">
+        <v>178</v>
+      </c>
+      <c r="E38" t="n">
+        <v>193</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>-2.03</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PNGO.JK</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3390</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3490</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>UVCR.JK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>222</v>
+      </c>
+      <c r="D40" t="n">
+        <v>226</v>
+      </c>
+      <c r="E40" t="n">
+        <v>230</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MCOL.JK</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4090</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3850</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3983.09</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>-2.61</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>RMKE.JK</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3190</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2760</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3260</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-13.48</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BSML.JK</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>414</v>
+      </c>
+      <c r="D43" t="n">
+        <v>416</v>
+      </c>
+      <c r="E43" t="n">
+        <v>424</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DRMA.JK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>990</v>
+      </c>
+      <c r="D44" t="n">
+        <v>980</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NTBK.JK</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>97</v>
+      </c>
+      <c r="D45" t="n">
+        <v>83</v>
+      </c>
+      <c r="E45" t="n">
+        <v>99</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>-14.43</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GULA.JK</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>412</v>
+      </c>
+      <c r="D46" t="n">
+        <v>416</v>
+      </c>
+      <c r="E46" t="n">
+        <v>432</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>KKES.JK</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>43</v>
+      </c>
+      <c r="D47" t="n">
+        <v>39</v>
+      </c>
+      <c r="E47" t="n">
+        <v>42</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ELPI.JK</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1425</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1380</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>-3.16</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MEDS.JK</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>98</v>
+      </c>
+      <c r="D49" t="n">
+        <v>90</v>
+      </c>
+      <c r="E49" t="n">
+        <v>118</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>20.41</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-8.16</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MMIX.JK</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>380</v>
+      </c>
+      <c r="D50" t="n">
+        <v>360</v>
+      </c>
+      <c r="E50" t="n">
+        <v>408</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>-5.26</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SMIL.JK</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>286</v>
+      </c>
+      <c r="D51" t="n">
+        <v>272</v>
+      </c>
+      <c r="E51" t="n">
+        <v>284</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>RGAS.JK</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>100</v>
+      </c>
+      <c r="D52" t="n">
+        <v>95</v>
+      </c>
+      <c r="E52" t="n">
+        <v>104</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>HYGN.JK</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>153</v>
+      </c>
+      <c r="D53" t="n">
+        <v>146</v>
+      </c>
+      <c r="E53" t="n">
+        <v>156</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-4.58</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>LABS.JK</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>162</v>
+      </c>
+      <c r="D54" t="n">
+        <v>153</v>
+      </c>
+      <c r="E54" t="n">
+        <v>184</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>-5.56</v>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>NEST.JK</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>500</v>
+      </c>
+      <c r="D55" t="n">
+        <v>505</v>
+      </c>
+      <c r="E55" t="n">
+        <v>515</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>ASPR.JK</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>PRE_MARKUP</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>396</v>
+      </c>
+      <c r="D56" t="n">
         <v>338</v>
       </c>
-      <c r="D15" t="n">
-        <v>288</v>
-      </c>
-      <c r="E15" t="n">
-        <v>378</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>-14.79</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="E56" t="n">
+        <v>338</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>-14.65</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>FORE.JK</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D57" t="n">
+        <v>910</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1005</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ASPI.JK</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>418</v>
+      </c>
+      <c r="D58" t="n">
+        <v>380</v>
+      </c>
+      <c r="E58" t="n">
+        <v>505</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>20.81</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-9.09</v>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CGAS.JK</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>168</v>
+      </c>
+      <c r="D59" t="n">
+        <v>159</v>
+      </c>
+      <c r="E59" t="n">
+        <v>173</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>KETR.JK</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PRE_MARKUP</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>615</v>
+      </c>
+      <c r="D60" t="n">
+        <v>565</v>
+      </c>
+      <c r="E60" t="n">
+        <v>625</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,7 +2913,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-05-21</t>
+          <t>Scalping — Review sesi market 2026-05-21</t>
         </is>
       </c>
     </row>

--- a/data/performance/daily/signal_list_2026-05-21.xlsx
+++ b/data/performance/daily/signal_list_2026-05-21.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-21.xlsx
+++ b/data/performance/daily/signal_list_2026-05-21.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-21.xlsx
+++ b/data/performance/daily/signal_list_2026-05-21.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:K60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -602,15 +613,20 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -644,15 +660,20 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>3.04</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -770,15 +801,20 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -812,15 +848,20 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -854,15 +895,20 @@
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -894,17 +940,22 @@
       <c r="G13" s="4" t="n">
         <v>-9.41</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -936,17 +987,22 @@
       <c r="G14" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,15 +1036,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1022,15 +1083,20 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1064,15 +1130,20 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1106,15 +1177,20 @@
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1146,17 +1222,22 @@
       <c r="G19" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1190,15 +1271,20 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1230,17 +1316,22 @@
       <c r="G21" s="4" t="n">
         <v>-4.71</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1272,17 +1363,22 @@
       <c r="G22" s="4" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1314,17 +1410,22 @@
       <c r="G23" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1358,15 +1459,20 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1400,15 +1506,20 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1440,17 +1551,22 @@
       <c r="G26" s="4" t="n">
         <v>-4.78</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1482,17 +1598,22 @@
       <c r="G27" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1526,15 +1647,20 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1568,15 +1694,20 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1610,15 +1741,20 @@
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1650,17 +1786,22 @@
       <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1692,17 +1833,22 @@
       <c r="G32" s="4" t="n">
         <v>7.41</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1736,15 +1882,20 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1778,15 +1929,20 @@
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1818,17 +1974,22 @@
       <c r="G35" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1860,17 +2021,22 @@
       <c r="G36" s="4" t="n">
         <v>-9.09</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1902,17 +2068,22 @@
       <c r="G37" s="4" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1944,17 +2115,22 @@
       <c r="G38" s="4" t="n">
         <v>-9.640000000000001</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1986,17 +2162,22 @@
       <c r="G39" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="H39" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2028,17 +2209,22 @@
       <c r="G40" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2070,17 +2256,22 @@
       <c r="G41" s="4" t="n">
         <v>-5.87</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2114,15 +2305,20 @@
       </c>
       <c r="H42" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2154,17 +2350,22 @@
       <c r="G43" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,15 +2399,20 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2240,15 +2446,20 @@
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2280,17 +2491,22 @@
       <c r="G46" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2322,17 +2538,22 @@
       <c r="G47" s="4" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2366,15 +2587,20 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2408,15 +2634,20 @@
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2450,15 +2681,20 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2490,17 +2726,22 @@
       <c r="G51" s="4" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2534,15 +2775,20 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2576,15 +2822,20 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2618,15 +2869,20 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2658,17 +2914,22 @@
       <c r="G55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2700,17 +2961,22 @@
       <c r="G56" s="4" t="n">
         <v>-14.65</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2744,15 +3010,20 @@
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2786,15 +3057,20 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2828,15 +3104,20 @@
       </c>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2870,15 +3151,20 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2895,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2905,9 +3191,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2937,7 +3224,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2962,15 +3249,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-21.xlsx
+++ b/data/performance/daily/signal_list_2026-05-21.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K60"/>
+  <dimension ref="A1:L60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1390</v>
       </c>
       <c r="D5" t="n">
+        <v>1390</v>
+      </c>
+      <c r="E5" t="n">
         <v>1340</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1405</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>1.08</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-3.6</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>2550</v>
       </c>
       <c r="D6" t="n">
+        <v>2580</v>
+      </c>
+      <c r="E6" t="n">
         <v>2540</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2620</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>4740</v>
       </c>
       <c r="D7" t="n">
+        <v>4760</v>
+      </c>
+      <c r="E7" t="n">
         <v>4620</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>4860</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.53</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-2.53</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>4740</v>
       </c>
       <c r="D8" t="n">
+        <v>4740</v>
+      </c>
+      <c r="E8" t="n">
         <v>4770</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>4790</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.05</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>2300</v>
       </c>
       <c r="D9" t="n">
-        <v>2370</v>
+        <v>2160</v>
       </c>
       <c r="E9" t="n">
         <v>2370</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>3.04</v>
+      <c r="F9" t="n">
+        <v>2370</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>3.04</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H9" s="4" t="n">
+        <v>3.04</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>340</v>
       </c>
       <c r="D10" t="n">
+        <v>344</v>
+      </c>
+      <c r="E10" t="n">
         <v>332</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>344</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.18</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-2.35</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>187</v>
       </c>
       <c r="D11" t="n">
+        <v>188</v>
+      </c>
+      <c r="E11" t="n">
         <v>176</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>195</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>4.28</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>-5.88</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>152</v>
       </c>
       <c r="D12" t="n">
+        <v>153</v>
+      </c>
+      <c r="E12" t="n">
         <v>150</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>155</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1.97</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-1.32</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>85</v>
       </c>
       <c r="D13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E13" t="n">
         <v>77</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>85</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-9.41</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>2230</v>
       </c>
       <c r="D14" t="n">
-        <v>2260</v>
+        <v>2230</v>
       </c>
       <c r="E14" t="n">
         <v>2260</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1.35</v>
+      <c r="F14" t="n">
+        <v>2260</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H14" s="4" t="n">
+        <v>1.35</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>16350</v>
       </c>
       <c r="D15" t="n">
+        <v>16350</v>
+      </c>
+      <c r="E15" t="n">
         <v>16200</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>16650</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1.83</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-0.92</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>113</v>
       </c>
       <c r="D16" t="n">
+        <v>113</v>
+      </c>
+      <c r="E16" t="n">
         <v>97</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>115</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>1.77</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-14.16</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>2150</v>
       </c>
       <c r="D17" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E17" t="n">
         <v>2080</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>2180</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-3.26</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>2820</v>
       </c>
       <c r="D18" t="n">
+        <v>2840</v>
+      </c>
+      <c r="E18" t="n">
         <v>2680</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>2960</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>4.96</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-4.96</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>1480</v>
       </c>
       <c r="D19" t="n">
+        <v>1480</v>
+      </c>
+      <c r="E19" t="n">
         <v>1485</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1495</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>0.34</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1261,30 +1312,33 @@
         <v>208</v>
       </c>
       <c r="E20" t="n">
+        <v>208</v>
+      </c>
+      <c r="F20" t="n">
         <v>228</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>510</v>
       </c>
       <c r="D21" t="n">
+        <v>510</v>
+      </c>
+      <c r="E21" t="n">
         <v>486</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>510</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>-4.71</v>
       </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1357,28 +1414,31 @@
       <c r="E22" t="n">
         <v>71</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>-8.970000000000001</v>
+      <c r="F22" t="n">
+        <v>71</v>
       </c>
       <c r="G22" s="4" t="n">
         <v>-8.970000000000001</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H22" s="4" t="n">
+        <v>-8.970000000000001</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>710.47</v>
       </c>
       <c r="D23" t="n">
+        <v>725</v>
+      </c>
+      <c r="E23" t="n">
         <v>715</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>730</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>2.75</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>0.64</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>2630</v>
       </c>
       <c r="D24" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E24" t="n">
         <v>2550</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>2640</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>0.38</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-3.04</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>7125</v>
       </c>
       <c r="D25" t="n">
+        <v>8475</v>
+      </c>
+      <c r="E25" t="n">
         <v>6500</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>8475</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>18.95</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-8.77</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>502</v>
       </c>
       <c r="D26" t="n">
+        <v>500</v>
+      </c>
+      <c r="E26" t="n">
         <v>478</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>500</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-4.78</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>100</v>
       </c>
       <c r="D27" t="n">
+        <v>104</v>
+      </c>
+      <c r="E27" t="n">
         <v>109</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>111</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>88</v>
       </c>
       <c r="D28" t="n">
+        <v>89</v>
+      </c>
+      <c r="E28" t="n">
         <v>87</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>96</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>9.09</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-1.14</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>79</v>
       </c>
       <c r="D29" t="n">
+        <v>79</v>
+      </c>
+      <c r="E29" t="n">
         <v>71</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>80</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>1.27</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-10.13</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>111</v>
       </c>
       <c r="D30" t="n">
+        <v>111</v>
+      </c>
+      <c r="E30" t="n">
         <v>108</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>113</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-2.7</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1780,28 +1864,31 @@
       <c r="E31" t="n">
         <v>1955</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>0</v>
+      <c r="F31" t="n">
+        <v>1955</v>
       </c>
       <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H31" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>162</v>
       </c>
       <c r="D32" t="n">
+        <v>161</v>
+      </c>
+      <c r="E32" t="n">
         <v>174</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>200</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>23.46</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>7.41</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>161</v>
       </c>
       <c r="D33" t="n">
+        <v>161</v>
+      </c>
+      <c r="E33" t="n">
         <v>155</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>164</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.86</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>-3.73</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>326</v>
       </c>
       <c r="D34" t="n">
+        <v>332</v>
+      </c>
+      <c r="E34" t="n">
         <v>322</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>332</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.84</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-1.23</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>800</v>
       </c>
       <c r="D35" t="n">
+        <v>775</v>
+      </c>
+      <c r="E35" t="n">
         <v>720</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>775</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>-3.12</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>44</v>
       </c>
       <c r="D36" t="n">
+        <v>44</v>
+      </c>
+      <c r="E36" t="n">
         <v>40</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>44</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-9.09</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2057,33 +2159,36 @@
         <v>218</v>
       </c>
       <c r="D37" t="n">
+        <v>214</v>
+      </c>
+      <c r="E37" t="n">
         <v>197</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>214</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>-1.83</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-9.630000000000001</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>197</v>
       </c>
       <c r="D38" t="n">
+        <v>193</v>
+      </c>
+      <c r="E38" t="n">
         <v>178</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>193</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>-2.03</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>-9.640000000000001</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2151,33 +2259,36 @@
         <v>3390</v>
       </c>
       <c r="D39" t="n">
+        <v>3390</v>
+      </c>
+      <c r="E39" t="n">
         <v>3400</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>3490</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>2.95</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,33 +2309,36 @@
         <v>222</v>
       </c>
       <c r="D40" t="n">
+        <v>222</v>
+      </c>
+      <c r="E40" t="n">
         <v>226</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>230</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>3.6</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2245,33 +2359,36 @@
         <v>4090</v>
       </c>
       <c r="D41" t="n">
+        <v>3888.02</v>
+      </c>
+      <c r="E41" t="n">
         <v>3850</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>3983.09</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>-2.61</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-5.87</v>
       </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2292,33 +2409,36 @@
         <v>3190</v>
       </c>
       <c r="D42" t="n">
+        <v>3210</v>
+      </c>
+      <c r="E42" t="n">
         <v>2760</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>3260</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>2.19</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-13.48</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2339,33 +2459,36 @@
         <v>414</v>
       </c>
       <c r="D43" t="n">
+        <v>420</v>
+      </c>
+      <c r="E43" t="n">
         <v>416</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>424</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>2.42</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2386,33 +2509,36 @@
         <v>990</v>
       </c>
       <c r="D44" t="n">
+        <v>990</v>
+      </c>
+      <c r="E44" t="n">
         <v>980</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>1000</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>-1.01</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2433,33 +2559,36 @@
         <v>97</v>
       </c>
       <c r="D45" t="n">
+        <v>97</v>
+      </c>
+      <c r="E45" t="n">
         <v>83</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>99</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>2.06</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-14.43</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2480,33 +2609,36 @@
         <v>412</v>
       </c>
       <c r="D46" t="n">
+        <v>410</v>
+      </c>
+      <c r="E46" t="n">
         <v>416</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>432</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>4.85</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>0.97</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2527,33 +2659,36 @@
         <v>43</v>
       </c>
       <c r="D47" t="n">
+        <v>42</v>
+      </c>
+      <c r="E47" t="n">
         <v>39</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>42</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>-2.33</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2574,33 +2709,36 @@
         <v>1425</v>
       </c>
       <c r="D48" t="n">
+        <v>1425</v>
+      </c>
+      <c r="E48" t="n">
         <v>1380</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>1445</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>-3.16</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,33 +2759,36 @@
         <v>98</v>
       </c>
       <c r="D49" t="n">
+        <v>100</v>
+      </c>
+      <c r="E49" t="n">
         <v>90</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>118</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>20.41</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>-8.16</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2668,33 +2809,36 @@
         <v>380</v>
       </c>
       <c r="D50" t="n">
+        <v>390</v>
+      </c>
+      <c r="E50" t="n">
         <v>360</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>408</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>7.37</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>-5.26</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2715,33 +2859,36 @@
         <v>286</v>
       </c>
       <c r="D51" t="n">
+        <v>284</v>
+      </c>
+      <c r="E51" t="n">
         <v>272</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>284</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>-4.9</v>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2762,33 +2909,36 @@
         <v>100</v>
       </c>
       <c r="D52" t="n">
+        <v>100</v>
+      </c>
+      <c r="E52" t="n">
         <v>95</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>104</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2809,33 +2959,36 @@
         <v>153</v>
       </c>
       <c r="D53" t="n">
+        <v>153</v>
+      </c>
+      <c r="E53" t="n">
         <v>146</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>156</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>1.96</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-4.58</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2856,33 +3009,36 @@
         <v>162</v>
       </c>
       <c r="D54" t="n">
+        <v>162</v>
+      </c>
+      <c r="E54" t="n">
         <v>153</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>184</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>13.58</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>-5.56</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2903,33 +3059,36 @@
         <v>500</v>
       </c>
       <c r="D55" t="n">
+        <v>515</v>
+      </c>
+      <c r="E55" t="n">
         <v>505</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>515</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2955,28 +3114,31 @@
       <c r="E56" t="n">
         <v>338</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>-14.65</v>
+      <c r="F56" t="n">
+        <v>338</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>-14.65</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H56" s="4" t="n">
+        <v>-14.65</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2997,33 +3159,36 @@
         <v>1000</v>
       </c>
       <c r="D57" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E57" t="n">
         <v>910</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>1005</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>0.5</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,33 +3209,36 @@
         <v>418</v>
       </c>
       <c r="D58" t="n">
+        <v>432</v>
+      </c>
+      <c r="E58" t="n">
         <v>380</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>505</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>20.81</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>-9.09</v>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3091,33 +3259,36 @@
         <v>168</v>
       </c>
       <c r="D59" t="n">
+        <v>169</v>
+      </c>
+      <c r="E59" t="n">
         <v>159</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>173</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>2.98</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>-5.36</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3138,33 +3309,36 @@
         <v>615</v>
       </c>
       <c r="D60" t="n">
+        <v>620</v>
+      </c>
+      <c r="E60" t="n">
         <v>565</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>625</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>-8.130000000000001</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3181,7 +3355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3189,12 +3363,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3224,45 +3399,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
